--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0502</v>
+        <v>3.011</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2754</v>
+        <v>6.5207</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.2251</v>
+        <v>-3.5096</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3021</v>
+        <v>0.306</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8859</v>
+        <v>-0.9473</v>
       </c>
       <c r="I2" t="n">
-        <v>1.188</v>
+        <v>1.2534</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7105</v>
+        <v>3.9309</v>
       </c>
       <c r="K2" t="n">
-        <v>1.3432</v>
+        <v>1.442</v>
       </c>
       <c r="L2" t="n">
-        <v>2.3673</v>
+        <v>2.4888</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.4084</v>
+        <v>-3.6249</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.2291</v>
+        <v>-2.3894</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1793</v>
+        <v>-1.2355</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1726</v>
+        <v>-0.1487</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3651</v>
+        <v>1.3687</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5377</v>
+        <v>-1.5174</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9201</v>
+        <v>0.9063</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2796</v>
+        <v>-0.3147</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7536</v>
+        <v>0.7107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0177</v>
+        <v>0.0282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7359</v>
+        <v>0.6825</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3537</v>
+        <v>0.3242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0026</v>
+        <v>-0.0226</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3512</v>
+        <v>0.3469</v>
       </c>
       <c r="J3" t="n">
-        <v>0.14</v>
+        <v>0.1426</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06</v>
+        <v>0.0616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2138</v>
+        <v>0.1816</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0574</v>
+        <v>-0.0842</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1222</v>
+        <v>-0.1144</v>
       </c>
       <c r="U3" t="n">
-        <v>0.122</v>
+        <v>0.1114</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4476</v>
+        <v>-0.3149</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7681</v>
+        <v>1.2622</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2157</v>
+        <v>-1.5771</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3053</v>
+        <v>-0.2369</v>
       </c>
       <c r="H4" t="n">
-        <v>2.468</v>
+        <v>2.5463</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.7733</v>
+        <v>-2.7832</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0319</v>
+        <v>3.3222</v>
       </c>
       <c r="K4" t="n">
-        <v>4.226</v>
+        <v>4.4646</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1941</v>
+        <v>-1.1425</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3372</v>
+        <v>-3.5591</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.758</v>
+        <v>-1.9183</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5792</v>
+        <v>-1.6407</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6007</v>
+        <v>2.5316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0384</v>
+        <v>0.0341</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4421</v>
+        <v>-0.3931</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4805</v>
+        <v>0.4272</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4194</v>
+        <v>0.4721</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3793</v>
+        <v>1.449</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9598</v>
+        <v>-0.9768</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0408</v>
+        <v>-1.0325</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.796</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2448</v>
+        <v>-0.2749</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8667</v>
+        <v>-0.8655</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4668</v>
+        <v>-0.4603</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3381</v>
+        <v>-0.3156</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3381</v>
+        <v>-0.3156</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5286</v>
+        <v>-0.55</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3999</v>
+        <v>-0.4053</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3741</v>
+        <v>-0.3617</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2578</v>
+        <v>-0.2473</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1163</v>
+        <v>-0.1144</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.088</v>
+        <v>-1.179</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8944</v>
+        <v>-0.7794</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1936</v>
+        <v>-0.3997</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4415</v>
+        <v>-1.4992</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1563</v>
+        <v>0.0974</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5979</v>
+        <v>-1.5966</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3236</v>
+        <v>0.3863</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9997</v>
+        <v>1.0263</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6761</v>
+        <v>-0.6401</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7651</v>
+        <v>-1.8854</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8434</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9218</v>
+        <v>-0.9565</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5873</v>
+        <v>-1.5425</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.218</v>
+        <v>-1.1656</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3693</v>
+        <v>-0.3768</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1442</v>
+        <v>-1.2259</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0495</v>
+        <v>-1.9889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9053</v>
+        <v>0.763</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7332</v>
+        <v>-2.7521</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3978</v>
+        <v>-1.4035</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3354</v>
+        <v>-1.3487</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.954</v>
+        <v>-1.9114</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.276</v>
+        <v>-1.2469</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7792</v>
+        <v>-0.8407</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1218</v>
+        <v>-0.1565</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2318</v>
+        <v>-0.2196</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0955</v>
+        <v>-0.0775</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1363</v>
+        <v>-0.142</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1001</v>
+        <v>-2.2773</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2245</v>
+        <v>0.2488</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3246</v>
+        <v>-2.5261</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4519</v>
+        <v>-2.5684</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2902</v>
+        <v>-1.3686</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1617</v>
+        <v>-1.1997</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3199</v>
+        <v>0.3263</v>
       </c>
       <c r="K8" t="n">
-        <v>0.16</v>
+        <v>0.1642</v>
       </c>
       <c r="L8" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.7718</v>
+        <v>-2.8947</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4501</v>
+        <v>-1.5329</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3217</v>
+        <v>-1.3618</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7291</v>
+        <v>-0.7079</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0955</v>
+        <v>-0.0775</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.6304</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2652</v>
+        <v>-3.0469</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6667</v>
+        <v>-1.083</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5985</v>
+        <v>-1.9638</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0615</v>
+        <v>-3.9755</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.1851</v>
+        <v>-5.1591</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1236</v>
+        <v>1.1836</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4738</v>
+        <v>-0.1204</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.441</v>
+        <v>-3.2172</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9672</v>
+        <v>3.0967</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5877</v>
+        <v>-3.8551</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7442</v>
+        <v>-1.942</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8435</v>
+        <v>-1.9131</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.7031</v>
+        <v>-2.6214</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5713</v>
+        <v>-1.4905</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1318</v>
+        <v>-1.1309</v>
       </c>
       <c r="V9" t="n">
-        <v>2.8993</v>
+        <v>2.9658</v>
       </c>
       <c r="W9" t="n">
-        <v>2.579</v>
+        <v>2.67</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3203</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.0807</v>
+        <v>-8.0944</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1425</v>
+        <v>-5.9256</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9382</v>
+        <v>-2.1688</v>
       </c>
       <c r="G10" t="n">
-        <v>-6.1736</v>
+        <v>-6.1823</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.9553</v>
+        <v>-3.9974</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2184</v>
+        <v>-2.1848</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.6222</v>
+        <v>-4.4784</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.1901</v>
+        <v>-3.1173</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4322</v>
+        <v>-1.3612</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5514</v>
+        <v>-1.7038</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7652</v>
+        <v>-0.8802</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7475000000000001</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3199</v>
+        <v>-0.2787</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4276</v>
+        <v>-0.4355</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5597</v>
+        <v>-1.5874</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5597</v>
+        <v>-1.5874</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.711</v>
+        <v>-8.609500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.922</v>
+        <v>-5.5469</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.789</v>
+        <v>-3.0626</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.8232</v>
+        <v>-6.7747</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.8676</v>
+        <v>-2.8115</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9556</v>
+        <v>-3.9632</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7572</v>
+        <v>-3.4814</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.2452</v>
+        <v>-1.026</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.512</v>
+        <v>-2.4554</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.066</v>
+        <v>-3.2932</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6224</v>
+        <v>-1.7854</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4436</v>
+        <v>-1.5078</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3278</v>
+        <v>-1.2738</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0358</v>
+        <v>0.0766</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3636</v>
+        <v>-1.3504</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3599</v>
+        <v>-0.3663</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.0738</v>
+        <v>-22.0587</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.1854</v>
+        <v>-8.0215</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.8883</v>
+        <v>-14.0371</v>
       </c>
       <c r="G12" t="n">
-        <v>-24.2011</v>
+        <v>-24.2244</v>
       </c>
       <c r="H12" t="n">
-        <v>-13.4218</v>
+        <v>-13.5266</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.7794</v>
+        <v>-10.6976</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.619400000000001</v>
+        <v>-2.1989</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.7015</v>
+        <v>-1.764300000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9178999999999995</v>
+        <v>-0.4350000000000005</v>
       </c>
       <c r="M12" t="n">
-        <v>-20.5816</v>
+        <v>-22.0253</v>
       </c>
       <c r="N12" t="n">
-        <v>-10.7203</v>
+        <v>-11.7625</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.8614</v>
+        <v>-10.2627</v>
       </c>
       <c r="P12" t="n">
-        <v>8.0023</v>
+        <v>7.7896</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.0025</v>
+        <v>-8.763100000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>17.0049</v>
+        <v>16.5528</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.835099999999999</v>
+        <v>-7.5587</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.7214</v>
+        <v>-2.3993</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1137</v>
+        <v>-5.1592</v>
       </c>
       <c r="V12" t="n">
-        <v>1.9602</v>
+        <v>1.9346</v>
       </c>
       <c r="W12" t="n">
-        <v>5.1581</v>
+        <v>5.3401</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.1977</v>
+        <v>-3.4053</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_PERFUMERIAS AVENIDA XOBORG.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.011</v>
+        <v>2.6634</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5207</v>
+        <v>5.5239</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.5096</v>
+        <v>-2.8605</v>
       </c>
       <c r="G2" t="n">
         <v>0.306</v>
@@ -610,13 +610,13 @@
         <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1487</v>
+        <v>-0.4963</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3687</v>
+        <v>0.372</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.5174</v>
+        <v>-0.8683</v>
       </c>
       <c r="V2" t="n">
         <v>0.9063</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7107</v>
+        <v>0.8598</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0282</v>
+        <v>0.1279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6825</v>
+        <v>0.7319</v>
       </c>
       <c r="G3" t="n">
         <v>0.3242</v>
@@ -688,13 +688,13 @@
         <v>0.3895</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.003</v>
+        <v>0.1461</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1144</v>
+        <v>-0.0148</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1114</v>
+        <v>0.1608</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3149</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2622</v>
+        <v>1.3619</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5771</v>
+        <v>-1.8957</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2369</v>
@@ -766,13 +766,13 @@
         <v>2.5316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0341</v>
+        <v>-0.1848</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3931</v>
+        <v>-0.2935</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4272</v>
+        <v>0.1087</v>
       </c>
       <c r="V4" t="n">
         <v>0.4721</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>M. MELGAR ZORITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0325</v>
+        <v>-0.598</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7576000000000001</v>
+        <v>-0.3807</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2749</v>
+        <v>-0.2173</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8655</v>
+        <v>-1.4992</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4603</v>
+        <v>0.0974</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4053</v>
+        <v>-1.5966</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3156</v>
+        <v>0.3863</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3156</v>
+        <v>1.0263</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6401</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.55</v>
+        <v>-1.8854</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1447</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4053</v>
+        <v>-0.9565</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1947</v>
+        <v>2.1421</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3895</v>
+        <v>2.1421</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3617</v>
+        <v>-0.9614</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2473</v>
+        <v>-0.7669</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1144</v>
+        <v>-0.1945</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MELGAR ZORITA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.179</v>
+        <v>-0.8053</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7794</v>
+        <v>-0.5583</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3997</v>
+        <v>-0.247</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4992</v>
+        <v>-0.8655</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0974</v>
+        <v>-0.4603</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5966</v>
+        <v>-0.4053</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3863</v>
+        <v>-0.3156</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0263</v>
+        <v>-0.3156</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6401</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8854</v>
+        <v>-0.55</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.1447</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9565</v>
+        <v>-0.4053</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1421</v>
+        <v>0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1421</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5425</v>
+        <v>-0.1345</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1656</v>
+        <v>-0.048</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3768</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2259</v>
+        <v>-1.3642</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9889</v>
+        <v>-2.288</v>
       </c>
       <c r="F7" t="n">
-        <v>0.763</v>
+        <v>0.9237</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7521</v>
@@ -1000,13 +1000,13 @@
         <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2196</v>
+        <v>-0.3579</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0775</v>
+        <v>-0.3765</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.142</v>
+        <v>0.0187</v>
       </c>
       <c r="V7" t="n">
         <v>0.3826</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2773</v>
+        <v>-1.4234</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2488</v>
+        <v>-0.1859</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5261</v>
+        <v>-1.2375</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5684</v>
+        <v>-3.9755</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3686</v>
+        <v>-5.1591</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1997</v>
+        <v>1.1836</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3263</v>
+        <v>-0.1204</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1642</v>
+        <v>-3.2172</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1621</v>
+        <v>3.0967</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.8947</v>
+        <v>-3.8551</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5329</v>
+        <v>-1.942</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3618</v>
+        <v>-1.9131</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5579</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5579</v>
+        <v>2.7263</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7079</v>
+        <v>-0.9979</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0775</v>
+        <v>-0.5934</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6304</v>
+        <v>-0.4045</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>2.9658</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0469</v>
+        <v>-2.2108</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.083</v>
+        <v>0.0495</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9638</v>
+        <v>-2.2603</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.9755</v>
+        <v>-2.5684</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.1591</v>
+        <v>-1.3686</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1836</v>
+        <v>-1.1997</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1204</v>
+        <v>0.3263</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.2172</v>
+        <v>0.1642</v>
       </c>
       <c r="L9" t="n">
-        <v>3.0967</v>
+        <v>0.1621</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8551</v>
+        <v>-2.8947</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.942</v>
+        <v>-1.5329</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9131</v>
+        <v>-1.3618</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1421</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7263</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.6214</v>
+        <v>-0.6414</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.4905</v>
+        <v>-0.2769</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1309</v>
+        <v>-0.3646</v>
       </c>
       <c r="V9" t="n">
-        <v>2.9658</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2958</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.0944</v>
+        <v>-7.7011</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9256</v>
+        <v>-5.8259</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1688</v>
+        <v>-1.8752</v>
       </c>
       <c r="G10" t="n">
         <v>-6.1823</v>
@@ -1234,13 +1234,13 @@
         <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.3209</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2787</v>
+        <v>-0.179</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4355</v>
+        <v>-0.1419</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5874</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.609500000000001</v>
+        <v>-8.2873</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.5469</v>
+        <v>-5.8459</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0626</v>
+        <v>-2.4413</v>
       </c>
       <c r="G11" t="n">
         <v>-6.7747</v>
@@ -1312,13 +1312,13 @@
         <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2738</v>
+        <v>-0.9515</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0766</v>
+        <v>-0.2224</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3504</v>
+        <v>-0.7291</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3663</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.0587</v>
+        <v>-19.4007</v>
       </c>
       <c r="E12" t="n">
         <v>-8.0215</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.0371</v>
+        <v>-11.3792</v>
       </c>
       <c r="G12" t="n">
         <v>-24.2244</v>
@@ -1363,13 +1363,13 @@
         <v>-10.6976</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1989</v>
+        <v>-2.198899999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.764300000000001</v>
+        <v>-1.7643</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4350000000000005</v>
+        <v>-0.4349999999999996</v>
       </c>
       <c r="M12" t="n">
         <v>-22.0253</v>
@@ -1390,13 +1390,13 @@
         <v>16.5528</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.5587</v>
+        <v>-4.9005</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3993</v>
+        <v>-2.3994</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1592</v>
+        <v>-2.5012</v>
       </c>
       <c r="V12" t="n">
         <v>1.9346</v>
